--- a/territory3.xlsx
+++ b/territory3.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7F7DBE-500B-4F10-ACCE-CAAA461E6B83}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67B51EF-4EDC-4D33-A2B0-AA6FCDB72B33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" activeTab="5" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" activeTab="6" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
   </bookViews>
   <sheets>
     <sheet name="mun" sheetId="3" r:id="rId1"/>
     <sheet name="Feuil2" sheetId="10" r:id="rId2"/>
     <sheet name="waste_gen" sheetId="1" r:id="rId3"/>
     <sheet name="dist" sheetId="6" r:id="rId4"/>
-    <sheet name="tech_pot" sheetId="9" r:id="rId5"/>
-    <sheet name="market" sheetId="8" r:id="rId6"/>
-    <sheet name="Feuil4" sheetId="12" r:id="rId7"/>
-    <sheet name="dist_market" sheetId="4" r:id="rId8"/>
+    <sheet name="market" sheetId="8" r:id="rId5"/>
+    <sheet name="tech_pot" sheetId="9" r:id="rId6"/>
+    <sheet name="dist_market" sheetId="4" r:id="rId7"/>
+    <sheet name="Feuil4" sheetId="12" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -723,171 +723,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DCAE16-4335-49F9-8C26-3341265BB48C}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1">
-        <v>1</v>
-      </c>
-      <c r="K1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="J16">
-        <f>11*20*12</f>
-        <v>2640</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C462B02-F830-4504-8CFB-862612762922}">
   <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1085,7 +920,406 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DCAE16-4335-49F9-8C26-3341265BB48C}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1">
+        <v>1</v>
+      </c>
+      <c r="K1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J16">
+        <f>11*20*12</f>
+        <v>2640</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08958C74-E6C0-46D4-987A-6DEF0A0AB368}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>50</v>
+      </c>
+      <c r="I2">
+        <v>60</v>
+      </c>
+      <c r="J2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <v>50</v>
+      </c>
+      <c r="H3">
+        <v>95</v>
+      </c>
+      <c r="I3">
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>40</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>69</v>
+      </c>
+      <c r="I4">
+        <v>47</v>
+      </c>
+      <c r="J4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>30</v>
+      </c>
+      <c r="H5">
+        <v>74</v>
+      </c>
+      <c r="I5">
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>25</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>60</v>
+      </c>
+      <c r="I7">
+        <v>35</v>
+      </c>
+      <c r="J7">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992B2B0E-AECF-41DB-AC20-A757648DB06D}">
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1294,238 +1528,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08958C74-E6C0-46D4-987A-6DEF0A0AB368}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>30</v>
-      </c>
-      <c r="D2">
-        <v>25</v>
-      </c>
-      <c r="E2">
-        <v>20</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>50</v>
-      </c>
-      <c r="I2">
-        <v>60</v>
-      </c>
-      <c r="J2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>30</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>100</v>
-      </c>
-      <c r="G3">
-        <v>50</v>
-      </c>
-      <c r="H3">
-        <v>95</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>25</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>40</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4">
-        <v>10</v>
-      </c>
-      <c r="H4">
-        <v>69</v>
-      </c>
-      <c r="I4">
-        <v>47</v>
-      </c>
-      <c r="J4">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>40</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5">
-        <v>30</v>
-      </c>
-      <c r="H5">
-        <v>74</v>
-      </c>
-      <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>100</v>
-      </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
-        <v>20</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>50</v>
-      </c>
-      <c r="H6">
-        <v>20</v>
-      </c>
-      <c r="I6">
-        <v>25</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>60</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>96</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>